--- a/tables/Table_S2.xlsx
+++ b/tables/Table_S2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2256">
   <si>
     <t xml:space="preserve">Target_gene_name</t>
   </si>
@@ -5790,6 +5790,12 @@
   </si>
   <si>
     <t xml:space="preserve">Q9P0U3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENP7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9BQF6</t>
   </si>
   <si>
     <t xml:space="preserve">SERPINA6</t>
@@ -19864,7 +19870,7 @@
         <v>1927</v>
       </c>
       <c r="C912" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D912" t="s">
         <v>7</v>
@@ -19878,10 +19884,10 @@
         <v>1929</v>
       </c>
       <c r="C913" t="s">
-        <v>1425</v>
+        <v>6</v>
       </c>
       <c r="D913" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="914">
@@ -19892,10 +19898,10 @@
         <v>1931</v>
       </c>
       <c r="C914" t="s">
-        <v>6</v>
+        <v>1425</v>
       </c>
       <c r="D914" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="915">
@@ -19906,7 +19912,7 @@
         <v>1933</v>
       </c>
       <c r="C915" t="s">
-        <v>1418</v>
+        <v>6</v>
       </c>
       <c r="D915" t="s">
         <v>7</v>
@@ -19920,10 +19926,10 @@
         <v>1935</v>
       </c>
       <c r="C916" t="s">
-        <v>10</v>
+        <v>1418</v>
       </c>
       <c r="D916" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="917">
@@ -19934,10 +19940,10 @@
         <v>1937</v>
       </c>
       <c r="C917" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D917" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="918">
@@ -19948,7 +19954,7 @@
         <v>1939</v>
       </c>
       <c r="C918" t="s">
-        <v>1100</v>
+        <v>6</v>
       </c>
       <c r="D918" t="s">
         <v>7</v>
@@ -19962,10 +19968,10 @@
         <v>1941</v>
       </c>
       <c r="C919" t="s">
-        <v>334</v>
+        <v>1100</v>
       </c>
       <c r="D919" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="920">
@@ -19976,10 +19982,10 @@
         <v>1943</v>
       </c>
       <c r="C920" t="s">
-        <v>198</v>
+        <v>334</v>
       </c>
       <c r="D920" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="921">
@@ -19990,7 +19996,7 @@
         <v>1945</v>
       </c>
       <c r="C921" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="D921" t="s">
         <v>7</v>
@@ -20004,7 +20010,7 @@
         <v>1947</v>
       </c>
       <c r="C922" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D922" t="s">
         <v>7</v>
@@ -20032,7 +20038,7 @@
         <v>1951</v>
       </c>
       <c r="C924" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D924" t="s">
         <v>7</v>
@@ -20046,7 +20052,7 @@
         <v>1953</v>
       </c>
       <c r="C925" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D925" t="s">
         <v>7</v>
@@ -20074,10 +20080,10 @@
         <v>1957</v>
       </c>
       <c r="C927" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D927" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="928">
@@ -20088,10 +20094,10 @@
         <v>1959</v>
       </c>
       <c r="C928" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D928" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="929">
@@ -20102,7 +20108,7 @@
         <v>1961</v>
       </c>
       <c r="C929" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D929" t="s">
         <v>7</v>
@@ -20116,7 +20122,7 @@
         <v>1963</v>
       </c>
       <c r="C930" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="D930" t="s">
         <v>7</v>
@@ -20130,7 +20136,7 @@
         <v>1965</v>
       </c>
       <c r="C931" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="D931" t="s">
         <v>7</v>
@@ -20144,7 +20150,7 @@
         <v>1967</v>
       </c>
       <c r="C932" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D932" t="s">
         <v>7</v>
@@ -20172,7 +20178,7 @@
         <v>1971</v>
       </c>
       <c r="C934" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D934" t="s">
         <v>7</v>
@@ -20186,7 +20192,7 @@
         <v>1973</v>
       </c>
       <c r="C935" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D935" t="s">
         <v>7</v>
@@ -20228,7 +20234,7 @@
         <v>1979</v>
       </c>
       <c r="C938" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D938" t="s">
         <v>7</v>
@@ -20242,7 +20248,7 @@
         <v>1981</v>
       </c>
       <c r="C939" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D939" t="s">
         <v>7</v>
@@ -20256,7 +20262,7 @@
         <v>1983</v>
       </c>
       <c r="C940" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D940" t="s">
         <v>7</v>
@@ -20284,10 +20290,10 @@
         <v>1987</v>
       </c>
       <c r="C942" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D942" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="943">
@@ -20298,10 +20304,10 @@
         <v>1989</v>
       </c>
       <c r="C943" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="D943" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="944">
@@ -20312,7 +20318,7 @@
         <v>1991</v>
       </c>
       <c r="C944" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="D944" t="s">
         <v>7</v>
@@ -20326,7 +20332,7 @@
         <v>1993</v>
       </c>
       <c r="C945" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="D945" t="s">
         <v>7</v>
@@ -20340,7 +20346,7 @@
         <v>1995</v>
       </c>
       <c r="C946" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D946" t="s">
         <v>7</v>
@@ -20354,7 +20360,7 @@
         <v>1997</v>
       </c>
       <c r="C947" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D947" t="s">
         <v>7</v>
@@ -20368,7 +20374,7 @@
         <v>1999</v>
       </c>
       <c r="C948" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="D948" t="s">
         <v>7</v>
@@ -20382,7 +20388,7 @@
         <v>2001</v>
       </c>
       <c r="C949" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D949" t="s">
         <v>7</v>
@@ -20396,7 +20402,7 @@
         <v>2003</v>
       </c>
       <c r="C950" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D950" t="s">
         <v>7</v>
@@ -20410,7 +20416,7 @@
         <v>2005</v>
       </c>
       <c r="C951" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D951" t="s">
         <v>7</v>
@@ -20424,7 +20430,7 @@
         <v>2007</v>
       </c>
       <c r="C952" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="D952" t="s">
         <v>7</v>
@@ -20466,10 +20472,10 @@
         <v>2013</v>
       </c>
       <c r="C955" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="D955" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="956">
@@ -20494,10 +20500,10 @@
         <v>2017</v>
       </c>
       <c r="C957" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D957" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="958">
@@ -20508,7 +20514,7 @@
         <v>2019</v>
       </c>
       <c r="C958" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D958" t="s">
         <v>7</v>
@@ -20522,10 +20528,10 @@
         <v>2021</v>
       </c>
       <c r="C959" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="D959" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="960">
@@ -20536,7 +20542,7 @@
         <v>2023</v>
       </c>
       <c r="C960" t="s">
-        <v>1194</v>
+        <v>10</v>
       </c>
       <c r="D960" t="s">
         <v>11</v>
@@ -20550,21 +20556,21 @@
         <v>2025</v>
       </c>
       <c r="C961" t="s">
-        <v>2026</v>
+        <v>1194</v>
       </c>
       <c r="D961" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B962" t="s">
         <v>2027</v>
       </c>
-      <c r="B962" t="s">
+      <c r="C962" t="s">
         <v>2028</v>
-      </c>
-      <c r="C962" t="s">
-        <v>161</v>
       </c>
       <c r="D962" t="s">
         <v>7</v>
@@ -20578,10 +20584,10 @@
         <v>2030</v>
       </c>
       <c r="C963" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="D963" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="964">
@@ -20606,10 +20612,10 @@
         <v>2034</v>
       </c>
       <c r="C965" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D965" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="966">
@@ -20620,7 +20626,7 @@
         <v>2036</v>
       </c>
       <c r="C966" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D966" t="s">
         <v>7</v>
@@ -20634,7 +20640,7 @@
         <v>2038</v>
       </c>
       <c r="C967" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="D967" t="s">
         <v>7</v>
@@ -20648,7 +20654,7 @@
         <v>2040</v>
       </c>
       <c r="C968" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D968" t="s">
         <v>7</v>
@@ -20662,7 +20668,7 @@
         <v>2042</v>
       </c>
       <c r="C969" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D969" t="s">
         <v>7</v>
@@ -20676,7 +20682,7 @@
         <v>2044</v>
       </c>
       <c r="C970" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D970" t="s">
         <v>7</v>
@@ -20690,10 +20696,10 @@
         <v>2046</v>
       </c>
       <c r="C971" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D971" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="972">
@@ -20704,7 +20710,7 @@
         <v>2048</v>
       </c>
       <c r="C972" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="D972" t="s">
         <v>11</v>
@@ -20718,10 +20724,10 @@
         <v>2050</v>
       </c>
       <c r="C973" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="D973" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="974">
@@ -20746,7 +20752,7 @@
         <v>2054</v>
       </c>
       <c r="C975" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="D975" t="s">
         <v>7</v>
@@ -20858,10 +20864,10 @@
         <v>2070</v>
       </c>
       <c r="C983" t="s">
-        <v>85</v>
+        <v>1041</v>
       </c>
       <c r="D983" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="984">
@@ -20886,10 +20892,10 @@
         <v>2074</v>
       </c>
       <c r="C985" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D985" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="986">
@@ -20900,10 +20906,10 @@
         <v>2076</v>
       </c>
       <c r="C986" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D986" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="987">
@@ -20914,10 +20920,10 @@
         <v>2078</v>
       </c>
       <c r="C987" t="s">
-        <v>418</v>
+        <v>10</v>
       </c>
       <c r="D987" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="988">
@@ -20928,10 +20934,10 @@
         <v>2080</v>
       </c>
       <c r="C988" t="s">
-        <v>10</v>
+        <v>418</v>
       </c>
       <c r="D988" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="989">
@@ -20942,10 +20948,10 @@
         <v>2082</v>
       </c>
       <c r="C989" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D989" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="990">
@@ -20956,7 +20962,7 @@
         <v>2084</v>
       </c>
       <c r="C990" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D990" t="s">
         <v>7</v>
@@ -20970,7 +20976,7 @@
         <v>2086</v>
       </c>
       <c r="C991" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="D991" t="s">
         <v>7</v>
@@ -20984,7 +20990,7 @@
         <v>2088</v>
       </c>
       <c r="C992" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D992" t="s">
         <v>7</v>
@@ -20998,7 +21004,7 @@
         <v>2090</v>
       </c>
       <c r="C993" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="D993" t="s">
         <v>7</v>
@@ -21026,7 +21032,7 @@
         <v>2094</v>
       </c>
       <c r="C995" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D995" t="s">
         <v>7</v>
@@ -21040,7 +21046,7 @@
         <v>2096</v>
       </c>
       <c r="C996" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D996" t="s">
         <v>7</v>
@@ -21054,7 +21060,7 @@
         <v>2098</v>
       </c>
       <c r="C997" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D997" t="s">
         <v>7</v>
@@ -21068,7 +21074,7 @@
         <v>2100</v>
       </c>
       <c r="C998" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="D998" t="s">
         <v>7</v>
@@ -21082,7 +21088,7 @@
         <v>2102</v>
       </c>
       <c r="C999" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D999" t="s">
         <v>7</v>
@@ -21096,7 +21102,7 @@
         <v>2104</v>
       </c>
       <c r="C1000" t="s">
-        <v>1041</v>
+        <v>91</v>
       </c>
       <c r="D1000" t="s">
         <v>7</v>
@@ -21110,10 +21116,10 @@
         <v>2106</v>
       </c>
       <c r="C1001" t="s">
-        <v>1225</v>
+        <v>1041</v>
       </c>
       <c r="D1001" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1002">
@@ -21124,10 +21130,10 @@
         <v>2108</v>
       </c>
       <c r="C1002" t="s">
-        <v>6</v>
+        <v>1225</v>
       </c>
       <c r="D1002" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1003">
@@ -21138,7 +21144,7 @@
         <v>2110</v>
       </c>
       <c r="C1003" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="D1003" t="s">
         <v>7</v>
@@ -21152,10 +21158,10 @@
         <v>2112</v>
       </c>
       <c r="C1004" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="D1004" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1005">
@@ -21166,10 +21172,10 @@
         <v>2114</v>
       </c>
       <c r="C1005" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D1005" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1006">
@@ -21180,7 +21186,7 @@
         <v>2116</v>
       </c>
       <c r="C1006" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D1006" t="s">
         <v>7</v>
@@ -21208,10 +21214,10 @@
         <v>2120</v>
       </c>
       <c r="C1008" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D1008" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1009">
@@ -21222,10 +21228,10 @@
         <v>2122</v>
       </c>
       <c r="C1009" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="D1009" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1010">
@@ -21250,7 +21256,7 @@
         <v>2126</v>
       </c>
       <c r="C1011" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D1011" t="s">
         <v>7</v>
@@ -21264,7 +21270,7 @@
         <v>2128</v>
       </c>
       <c r="C1012" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="D1012" t="s">
         <v>7</v>
@@ -21278,7 +21284,7 @@
         <v>2130</v>
       </c>
       <c r="C1013" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="D1013" t="s">
         <v>7</v>
@@ -21292,7 +21298,7 @@
         <v>2132</v>
       </c>
       <c r="C1014" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D1014" t="s">
         <v>7</v>
@@ -21306,7 +21312,7 @@
         <v>2134</v>
       </c>
       <c r="C1015" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="D1015" t="s">
         <v>7</v>
@@ -21320,7 +21326,7 @@
         <v>2136</v>
       </c>
       <c r="C1016" t="s">
-        <v>502</v>
+        <v>6</v>
       </c>
       <c r="D1016" t="s">
         <v>7</v>
@@ -21334,10 +21340,10 @@
         <v>2138</v>
       </c>
       <c r="C1017" t="s">
-        <v>588</v>
+        <v>502</v>
       </c>
       <c r="D1017" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1018">
@@ -21348,10 +21354,10 @@
         <v>2140</v>
       </c>
       <c r="C1018" t="s">
-        <v>30</v>
+        <v>588</v>
       </c>
       <c r="D1018" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1019">
@@ -21362,7 +21368,7 @@
         <v>2142</v>
       </c>
       <c r="C1019" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="D1019" t="s">
         <v>7</v>
@@ -21376,7 +21382,7 @@
         <v>2144</v>
       </c>
       <c r="C1020" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="D1020" t="s">
         <v>7</v>
@@ -21390,7 +21396,7 @@
         <v>2146</v>
       </c>
       <c r="C1021" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="D1021" t="s">
         <v>7</v>
@@ -21404,24 +21410,24 @@
         <v>2148</v>
       </c>
       <c r="C1022" t="s">
-        <v>2149</v>
+        <v>30</v>
       </c>
       <c r="D1022" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1023" t="s">
         <v>2150</v>
       </c>
-      <c r="B1023" t="s">
+      <c r="C1023" t="s">
         <v>2151</v>
       </c>
-      <c r="C1023" t="s">
-        <v>44</v>
-      </c>
       <c r="D1023" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1024">
@@ -21432,7 +21438,7 @@
         <v>2153</v>
       </c>
       <c r="C1024" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D1024" t="s">
         <v>7</v>
@@ -21488,24 +21494,24 @@
         <v>2161</v>
       </c>
       <c r="C1028" t="s">
-        <v>2162</v>
+        <v>6</v>
       </c>
       <c r="D1028" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1029" t="s">
         <v>2163</v>
       </c>
-      <c r="B1029" t="s">
+      <c r="C1029" t="s">
         <v>2164</v>
       </c>
-      <c r="C1029" t="s">
-        <v>128</v>
-      </c>
       <c r="D1029" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1030">
@@ -21516,10 +21522,10 @@
         <v>2166</v>
       </c>
       <c r="C1030" t="s">
-        <v>553</v>
+        <v>128</v>
       </c>
       <c r="D1030" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1031">
@@ -21530,10 +21536,10 @@
         <v>2168</v>
       </c>
       <c r="C1031" t="s">
-        <v>6</v>
+        <v>553</v>
       </c>
       <c r="D1031" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1032">
@@ -21544,10 +21550,10 @@
         <v>2170</v>
       </c>
       <c r="C1032" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1032" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1033">
@@ -21558,10 +21564,10 @@
         <v>2172</v>
       </c>
       <c r="C1033" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D1033" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1034">
@@ -21572,7 +21578,7 @@
         <v>2174</v>
       </c>
       <c r="C1034" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D1034" t="s">
         <v>7</v>
@@ -21586,7 +21592,7 @@
         <v>2176</v>
       </c>
       <c r="C1035" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D1035" t="s">
         <v>7</v>
@@ -21600,10 +21606,10 @@
         <v>2178</v>
       </c>
       <c r="C1036" t="s">
-        <v>839</v>
+        <v>6</v>
       </c>
       <c r="D1036" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1037">
@@ -21614,10 +21620,10 @@
         <v>2180</v>
       </c>
       <c r="C1037" t="s">
-        <v>6</v>
+        <v>839</v>
       </c>
       <c r="D1037" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1038">
@@ -21642,10 +21648,10 @@
         <v>2184</v>
       </c>
       <c r="C1039" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="D1039" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1040">
@@ -21656,10 +21662,10 @@
         <v>2186</v>
       </c>
       <c r="C1040" t="s">
-        <v>6</v>
+        <v>263</v>
       </c>
       <c r="D1040" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1041">
@@ -21670,7 +21676,7 @@
         <v>2188</v>
       </c>
       <c r="C1041" t="s">
-        <v>2189</v>
+        <v>6</v>
       </c>
       <c r="D1041" t="s">
         <v>7</v>
@@ -21678,13 +21684,13 @@
     </row>
     <row r="1042">
       <c r="A1042" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1042" t="s">
         <v>2190</v>
       </c>
-      <c r="B1042" t="s">
+      <c r="C1042" t="s">
         <v>2191</v>
-      </c>
-      <c r="C1042" t="s">
-        <v>44</v>
       </c>
       <c r="D1042" t="s">
         <v>7</v>
@@ -21698,7 +21704,7 @@
         <v>2193</v>
       </c>
       <c r="C1043" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D1043" t="s">
         <v>7</v>
@@ -21740,7 +21746,7 @@
         <v>2199</v>
       </c>
       <c r="C1046" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="D1046" t="s">
         <v>7</v>
@@ -21754,7 +21760,7 @@
         <v>2201</v>
       </c>
       <c r="C1047" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="D1047" t="s">
         <v>7</v>
@@ -21768,7 +21774,7 @@
         <v>2203</v>
       </c>
       <c r="C1048" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="D1048" t="s">
         <v>7</v>
@@ -21782,10 +21788,10 @@
         <v>2205</v>
       </c>
       <c r="C1049" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1049" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1050">
@@ -21796,10 +21802,10 @@
         <v>2207</v>
       </c>
       <c r="C1050" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1050" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1051">
@@ -21810,7 +21816,7 @@
         <v>2209</v>
       </c>
       <c r="C1051" t="s">
-        <v>1041</v>
+        <v>6</v>
       </c>
       <c r="D1051" t="s">
         <v>7</v>
@@ -21824,7 +21830,7 @@
         <v>2211</v>
       </c>
       <c r="C1052" t="s">
-        <v>161</v>
+        <v>1041</v>
       </c>
       <c r="D1052" t="s">
         <v>7</v>
@@ -21852,10 +21858,10 @@
         <v>2215</v>
       </c>
       <c r="C1054" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="D1054" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1055">
@@ -21866,10 +21872,10 @@
         <v>2217</v>
       </c>
       <c r="C1055" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1055" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1056">
@@ -21880,10 +21886,10 @@
         <v>2219</v>
       </c>
       <c r="C1056" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1056" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1057">
@@ -21894,10 +21900,10 @@
         <v>2221</v>
       </c>
       <c r="C1057" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1057" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1058">
@@ -21908,7 +21914,7 @@
         <v>2223</v>
       </c>
       <c r="C1058" t="s">
-        <v>1725</v>
+        <v>6</v>
       </c>
       <c r="D1058" t="s">
         <v>7</v>
@@ -21922,10 +21928,10 @@
         <v>2225</v>
       </c>
       <c r="C1059" t="s">
-        <v>1194</v>
+        <v>1725</v>
       </c>
       <c r="D1059" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1060">
@@ -21936,10 +21942,10 @@
         <v>2227</v>
       </c>
       <c r="C1060" t="s">
-        <v>6</v>
+        <v>1194</v>
       </c>
       <c r="D1060" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1061">
@@ -21950,10 +21956,10 @@
         <v>2229</v>
       </c>
       <c r="C1061" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1061" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1062">
@@ -21964,10 +21970,10 @@
         <v>2231</v>
       </c>
       <c r="C1062" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D1062" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1063">
@@ -21978,10 +21984,10 @@
         <v>2233</v>
       </c>
       <c r="C1063" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D1063" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1064">
@@ -21992,10 +21998,10 @@
         <v>2235</v>
       </c>
       <c r="C1064" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="D1064" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1065">
@@ -22006,7 +22012,7 @@
         <v>2237</v>
       </c>
       <c r="C1065" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D1065" t="s">
         <v>7</v>
@@ -22020,10 +22026,10 @@
         <v>2239</v>
       </c>
       <c r="C1066" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D1066" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1067">
@@ -22034,10 +22040,10 @@
         <v>2241</v>
       </c>
       <c r="C1067" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1067" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1068">
@@ -22062,7 +22068,7 @@
         <v>2245</v>
       </c>
       <c r="C1069" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D1069" t="s">
         <v>7</v>
@@ -22076,7 +22082,7 @@
         <v>2247</v>
       </c>
       <c r="C1070" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D1070" t="s">
         <v>7</v>
@@ -22121,6 +22127,20 @@
         <v>6</v>
       </c>
       <c r="D1073" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1074" t="s">
         <v>7</v>
       </c>
     </row>

--- a/tables/Table_S2.xlsx
+++ b/tables/Table_S2.xlsx
@@ -6,13 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Table S2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Targets_ZWHQD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="2254">
   <si>
     <t xml:space="preserve">Target_gene_name</t>
   </si>
@@ -5790,12 +5790,6 @@
   </si>
   <si>
     <t xml:space="preserve">Q9P0U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENP7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9BQF6</t>
   </si>
   <si>
     <t xml:space="preserve">SERPINA6</t>
@@ -19870,7 +19864,7 @@
         <v>1927</v>
       </c>
       <c r="C912" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D912" t="s">
         <v>7</v>
@@ -19884,10 +19878,10 @@
         <v>1929</v>
       </c>
       <c r="C913" t="s">
-        <v>6</v>
+        <v>1425</v>
       </c>
       <c r="D913" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="914">
@@ -19898,10 +19892,10 @@
         <v>1931</v>
       </c>
       <c r="C914" t="s">
-        <v>1425</v>
+        <v>6</v>
       </c>
       <c r="D914" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="915">
@@ -19912,7 +19906,7 @@
         <v>1933</v>
       </c>
       <c r="C915" t="s">
-        <v>6</v>
+        <v>1418</v>
       </c>
       <c r="D915" t="s">
         <v>7</v>
@@ -19926,10 +19920,10 @@
         <v>1935</v>
       </c>
       <c r="C916" t="s">
-        <v>1418</v>
+        <v>10</v>
       </c>
       <c r="D916" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="917">
@@ -19940,10 +19934,10 @@
         <v>1937</v>
       </c>
       <c r="C917" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D917" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="918">
@@ -19954,7 +19948,7 @@
         <v>1939</v>
       </c>
       <c r="C918" t="s">
-        <v>6</v>
+        <v>1100</v>
       </c>
       <c r="D918" t="s">
         <v>7</v>
@@ -19968,10 +19962,10 @@
         <v>1941</v>
       </c>
       <c r="C919" t="s">
-        <v>1100</v>
+        <v>334</v>
       </c>
       <c r="D919" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="920">
@@ -19982,10 +19976,10 @@
         <v>1943</v>
       </c>
       <c r="C920" t="s">
-        <v>334</v>
+        <v>198</v>
       </c>
       <c r="D920" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="921">
@@ -19996,7 +19990,7 @@
         <v>1945</v>
       </c>
       <c r="C921" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="D921" t="s">
         <v>7</v>
@@ -20010,7 +20004,7 @@
         <v>1947</v>
       </c>
       <c r="C922" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D922" t="s">
         <v>7</v>
@@ -20038,7 +20032,7 @@
         <v>1951</v>
       </c>
       <c r="C924" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D924" t="s">
         <v>7</v>
@@ -20052,7 +20046,7 @@
         <v>1953</v>
       </c>
       <c r="C925" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D925" t="s">
         <v>7</v>
@@ -20080,10 +20074,10 @@
         <v>1957</v>
       </c>
       <c r="C927" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D927" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="928">
@@ -20094,10 +20088,10 @@
         <v>1959</v>
       </c>
       <c r="C928" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D928" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="929">
@@ -20108,7 +20102,7 @@
         <v>1961</v>
       </c>
       <c r="C929" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D929" t="s">
         <v>7</v>
@@ -20122,7 +20116,7 @@
         <v>1963</v>
       </c>
       <c r="C930" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="D930" t="s">
         <v>7</v>
@@ -20136,7 +20130,7 @@
         <v>1965</v>
       </c>
       <c r="C931" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="D931" t="s">
         <v>7</v>
@@ -20150,7 +20144,7 @@
         <v>1967</v>
       </c>
       <c r="C932" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D932" t="s">
         <v>7</v>
@@ -20178,7 +20172,7 @@
         <v>1971</v>
       </c>
       <c r="C934" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D934" t="s">
         <v>7</v>
@@ -20192,7 +20186,7 @@
         <v>1973</v>
       </c>
       <c r="C935" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D935" t="s">
         <v>7</v>
@@ -20234,7 +20228,7 @@
         <v>1979</v>
       </c>
       <c r="C938" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D938" t="s">
         <v>7</v>
@@ -20248,7 +20242,7 @@
         <v>1981</v>
       </c>
       <c r="C939" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D939" t="s">
         <v>7</v>
@@ -20262,7 +20256,7 @@
         <v>1983</v>
       </c>
       <c r="C940" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D940" t="s">
         <v>7</v>
@@ -20290,10 +20284,10 @@
         <v>1987</v>
       </c>
       <c r="C942" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D942" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="943">
@@ -20304,10 +20298,10 @@
         <v>1989</v>
       </c>
       <c r="C943" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="D943" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="944">
@@ -20318,7 +20312,7 @@
         <v>1991</v>
       </c>
       <c r="C944" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="D944" t="s">
         <v>7</v>
@@ -20332,7 +20326,7 @@
         <v>1993</v>
       </c>
       <c r="C945" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="D945" t="s">
         <v>7</v>
@@ -20346,7 +20340,7 @@
         <v>1995</v>
       </c>
       <c r="C946" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D946" t="s">
         <v>7</v>
@@ -20360,7 +20354,7 @@
         <v>1997</v>
       </c>
       <c r="C947" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="D947" t="s">
         <v>7</v>
@@ -20374,7 +20368,7 @@
         <v>1999</v>
       </c>
       <c r="C948" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D948" t="s">
         <v>7</v>
@@ -20388,7 +20382,7 @@
         <v>2001</v>
       </c>
       <c r="C949" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D949" t="s">
         <v>7</v>
@@ -20402,7 +20396,7 @@
         <v>2003</v>
       </c>
       <c r="C950" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D950" t="s">
         <v>7</v>
@@ -20416,7 +20410,7 @@
         <v>2005</v>
       </c>
       <c r="C951" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D951" t="s">
         <v>7</v>
@@ -20430,7 +20424,7 @@
         <v>2007</v>
       </c>
       <c r="C952" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="D952" t="s">
         <v>7</v>
@@ -20472,10 +20466,10 @@
         <v>2013</v>
       </c>
       <c r="C955" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="D955" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="956">
@@ -20500,10 +20494,10 @@
         <v>2017</v>
       </c>
       <c r="C957" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D957" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="958">
@@ -20514,7 +20508,7 @@
         <v>2019</v>
       </c>
       <c r="C958" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D958" t="s">
         <v>7</v>
@@ -20528,10 +20522,10 @@
         <v>2021</v>
       </c>
       <c r="C959" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="D959" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="960">
@@ -20542,7 +20536,7 @@
         <v>2023</v>
       </c>
       <c r="C960" t="s">
-        <v>10</v>
+        <v>1194</v>
       </c>
       <c r="D960" t="s">
         <v>11</v>
@@ -20556,21 +20550,21 @@
         <v>2025</v>
       </c>
       <c r="C961" t="s">
-        <v>1194</v>
+        <v>2026</v>
       </c>
       <c r="D961" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B962" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C962" t="s">
-        <v>2028</v>
+        <v>161</v>
       </c>
       <c r="D962" t="s">
         <v>7</v>
@@ -20584,10 +20578,10 @@
         <v>2030</v>
       </c>
       <c r="C963" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="D963" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="964">
@@ -20612,10 +20606,10 @@
         <v>2034</v>
       </c>
       <c r="C965" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D965" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="966">
@@ -20626,7 +20620,7 @@
         <v>2036</v>
       </c>
       <c r="C966" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="D966" t="s">
         <v>7</v>
@@ -20640,7 +20634,7 @@
         <v>2038</v>
       </c>
       <c r="C967" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="D967" t="s">
         <v>7</v>
@@ -20654,7 +20648,7 @@
         <v>2040</v>
       </c>
       <c r="C968" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="D968" t="s">
         <v>7</v>
@@ -20668,7 +20662,7 @@
         <v>2042</v>
       </c>
       <c r="C969" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D969" t="s">
         <v>7</v>
@@ -20682,7 +20676,7 @@
         <v>2044</v>
       </c>
       <c r="C970" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D970" t="s">
         <v>7</v>
@@ -20696,10 +20690,10 @@
         <v>2046</v>
       </c>
       <c r="C971" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D971" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="972">
@@ -20710,7 +20704,7 @@
         <v>2048</v>
       </c>
       <c r="C972" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="D972" t="s">
         <v>11</v>
@@ -20724,10 +20718,10 @@
         <v>2050</v>
       </c>
       <c r="C973" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="D973" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="974">
@@ -20752,7 +20746,7 @@
         <v>2054</v>
       </c>
       <c r="C975" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="D975" t="s">
         <v>7</v>
@@ -20864,10 +20858,10 @@
         <v>2070</v>
       </c>
       <c r="C983" t="s">
-        <v>1041</v>
+        <v>85</v>
       </c>
       <c r="D983" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="984">
@@ -20892,10 +20886,10 @@
         <v>2074</v>
       </c>
       <c r="C985" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="D985" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="986">
@@ -20906,10 +20900,10 @@
         <v>2076</v>
       </c>
       <c r="C986" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D986" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="987">
@@ -20920,10 +20914,10 @@
         <v>2078</v>
       </c>
       <c r="C987" t="s">
-        <v>10</v>
+        <v>418</v>
       </c>
       <c r="D987" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="988">
@@ -20934,10 +20928,10 @@
         <v>2080</v>
       </c>
       <c r="C988" t="s">
-        <v>418</v>
+        <v>10</v>
       </c>
       <c r="D988" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="989">
@@ -20948,10 +20942,10 @@
         <v>2082</v>
       </c>
       <c r="C989" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D989" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="990">
@@ -20962,7 +20956,7 @@
         <v>2084</v>
       </c>
       <c r="C990" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="D990" t="s">
         <v>7</v>
@@ -20976,7 +20970,7 @@
         <v>2086</v>
       </c>
       <c r="C991" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D991" t="s">
         <v>7</v>
@@ -20990,7 +20984,7 @@
         <v>2088</v>
       </c>
       <c r="C992" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="D992" t="s">
         <v>7</v>
@@ -21004,7 +20998,7 @@
         <v>2090</v>
       </c>
       <c r="C993" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D993" t="s">
         <v>7</v>
@@ -21032,7 +21026,7 @@
         <v>2094</v>
       </c>
       <c r="C995" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D995" t="s">
         <v>7</v>
@@ -21046,7 +21040,7 @@
         <v>2096</v>
       </c>
       <c r="C996" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D996" t="s">
         <v>7</v>
@@ -21060,7 +21054,7 @@
         <v>2098</v>
       </c>
       <c r="C997" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D997" t="s">
         <v>7</v>
@@ -21074,7 +21068,7 @@
         <v>2100</v>
       </c>
       <c r="C998" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="D998" t="s">
         <v>7</v>
@@ -21088,7 +21082,7 @@
         <v>2102</v>
       </c>
       <c r="C999" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="D999" t="s">
         <v>7</v>
@@ -21102,7 +21096,7 @@
         <v>2104</v>
       </c>
       <c r="C1000" t="s">
-        <v>91</v>
+        <v>1041</v>
       </c>
       <c r="D1000" t="s">
         <v>7</v>
@@ -21116,10 +21110,10 @@
         <v>2106</v>
       </c>
       <c r="C1001" t="s">
-        <v>1041</v>
+        <v>1225</v>
       </c>
       <c r="D1001" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1002">
@@ -21130,10 +21124,10 @@
         <v>2108</v>
       </c>
       <c r="C1002" t="s">
-        <v>1225</v>
+        <v>6</v>
       </c>
       <c r="D1002" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1003">
@@ -21144,7 +21138,7 @@
         <v>2110</v>
       </c>
       <c r="C1003" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="D1003" t="s">
         <v>7</v>
@@ -21158,10 +21152,10 @@
         <v>2112</v>
       </c>
       <c r="C1004" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="D1004" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1005">
@@ -21172,10 +21166,10 @@
         <v>2114</v>
       </c>
       <c r="C1005" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D1005" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1006">
@@ -21186,7 +21180,7 @@
         <v>2116</v>
       </c>
       <c r="C1006" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D1006" t="s">
         <v>7</v>
@@ -21214,10 +21208,10 @@
         <v>2120</v>
       </c>
       <c r="C1008" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D1008" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1009">
@@ -21228,10 +21222,10 @@
         <v>2122</v>
       </c>
       <c r="C1009" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="D1009" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1010">
@@ -21256,7 +21250,7 @@
         <v>2126</v>
       </c>
       <c r="C1011" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="D1011" t="s">
         <v>7</v>
@@ -21270,7 +21264,7 @@
         <v>2128</v>
       </c>
       <c r="C1012" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="D1012" t="s">
         <v>7</v>
@@ -21284,7 +21278,7 @@
         <v>2130</v>
       </c>
       <c r="C1013" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="D1013" t="s">
         <v>7</v>
@@ -21298,7 +21292,7 @@
         <v>2132</v>
       </c>
       <c r="C1014" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D1014" t="s">
         <v>7</v>
@@ -21312,7 +21306,7 @@
         <v>2134</v>
       </c>
       <c r="C1015" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="D1015" t="s">
         <v>7</v>
@@ -21326,7 +21320,7 @@
         <v>2136</v>
       </c>
       <c r="C1016" t="s">
-        <v>6</v>
+        <v>502</v>
       </c>
       <c r="D1016" t="s">
         <v>7</v>
@@ -21340,10 +21334,10 @@
         <v>2138</v>
       </c>
       <c r="C1017" t="s">
-        <v>502</v>
+        <v>588</v>
       </c>
       <c r="D1017" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1018">
@@ -21354,10 +21348,10 @@
         <v>2140</v>
       </c>
       <c r="C1018" t="s">
-        <v>588</v>
+        <v>30</v>
       </c>
       <c r="D1018" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1019">
@@ -21368,7 +21362,7 @@
         <v>2142</v>
       </c>
       <c r="C1019" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="D1019" t="s">
         <v>7</v>
@@ -21382,7 +21376,7 @@
         <v>2144</v>
       </c>
       <c r="C1020" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1020" t="s">
         <v>7</v>
@@ -21396,7 +21390,7 @@
         <v>2146</v>
       </c>
       <c r="C1021" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="D1021" t="s">
         <v>7</v>
@@ -21410,24 +21404,24 @@
         <v>2148</v>
       </c>
       <c r="C1022" t="s">
-        <v>30</v>
+        <v>2149</v>
       </c>
       <c r="D1022" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1023" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="C1023" t="s">
-        <v>2151</v>
+        <v>44</v>
       </c>
       <c r="D1023" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1024">
@@ -21438,7 +21432,7 @@
         <v>2153</v>
       </c>
       <c r="C1024" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D1024" t="s">
         <v>7</v>
@@ -21494,24 +21488,24 @@
         <v>2161</v>
       </c>
       <c r="C1028" t="s">
-        <v>6</v>
+        <v>2162</v>
       </c>
       <c r="D1028" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="B1029" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C1029" t="s">
-        <v>2164</v>
+        <v>128</v>
       </c>
       <c r="D1029" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1030">
@@ -21522,10 +21516,10 @@
         <v>2166</v>
       </c>
       <c r="C1030" t="s">
-        <v>128</v>
+        <v>553</v>
       </c>
       <c r="D1030" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1031">
@@ -21536,10 +21530,10 @@
         <v>2168</v>
       </c>
       <c r="C1031" t="s">
-        <v>553</v>
+        <v>6</v>
       </c>
       <c r="D1031" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1032">
@@ -21550,10 +21544,10 @@
         <v>2170</v>
       </c>
       <c r="C1032" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1032" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1033">
@@ -21564,10 +21558,10 @@
         <v>2172</v>
       </c>
       <c r="C1033" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D1033" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1034">
@@ -21578,7 +21572,7 @@
         <v>2174</v>
       </c>
       <c r="C1034" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D1034" t="s">
         <v>7</v>
@@ -21592,7 +21586,7 @@
         <v>2176</v>
       </c>
       <c r="C1035" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D1035" t="s">
         <v>7</v>
@@ -21606,10 +21600,10 @@
         <v>2178</v>
       </c>
       <c r="C1036" t="s">
-        <v>6</v>
+        <v>839</v>
       </c>
       <c r="D1036" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1037">
@@ -21620,10 +21614,10 @@
         <v>2180</v>
       </c>
       <c r="C1037" t="s">
-        <v>839</v>
+        <v>6</v>
       </c>
       <c r="D1037" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1038">
@@ -21648,10 +21642,10 @@
         <v>2184</v>
       </c>
       <c r="C1039" t="s">
-        <v>6</v>
+        <v>263</v>
       </c>
       <c r="D1039" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1040">
@@ -21662,10 +21656,10 @@
         <v>2186</v>
       </c>
       <c r="C1040" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="D1040" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1041">
@@ -21676,7 +21670,7 @@
         <v>2188</v>
       </c>
       <c r="C1041" t="s">
-        <v>6</v>
+        <v>2189</v>
       </c>
       <c r="D1041" t="s">
         <v>7</v>
@@ -21684,13 +21678,13 @@
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B1042" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C1042" t="s">
-        <v>2191</v>
+        <v>44</v>
       </c>
       <c r="D1042" t="s">
         <v>7</v>
@@ -21704,7 +21698,7 @@
         <v>2193</v>
       </c>
       <c r="C1043" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D1043" t="s">
         <v>7</v>
@@ -21746,7 +21740,7 @@
         <v>2199</v>
       </c>
       <c r="C1046" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D1046" t="s">
         <v>7</v>
@@ -21760,7 +21754,7 @@
         <v>2201</v>
       </c>
       <c r="C1047" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="D1047" t="s">
         <v>7</v>
@@ -21774,7 +21768,7 @@
         <v>2203</v>
       </c>
       <c r="C1048" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="D1048" t="s">
         <v>7</v>
@@ -21788,10 +21782,10 @@
         <v>2205</v>
       </c>
       <c r="C1049" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1049" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1050">
@@ -21802,10 +21796,10 @@
         <v>2207</v>
       </c>
       <c r="C1050" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1050" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1051">
@@ -21816,7 +21810,7 @@
         <v>2209</v>
       </c>
       <c r="C1051" t="s">
-        <v>6</v>
+        <v>1041</v>
       </c>
       <c r="D1051" t="s">
         <v>7</v>
@@ -21830,7 +21824,7 @@
         <v>2211</v>
       </c>
       <c r="C1052" t="s">
-        <v>1041</v>
+        <v>161</v>
       </c>
       <c r="D1052" t="s">
         <v>7</v>
@@ -21858,10 +21852,10 @@
         <v>2215</v>
       </c>
       <c r="C1054" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="D1054" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1055">
@@ -21872,10 +21866,10 @@
         <v>2217</v>
       </c>
       <c r="C1055" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1055" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1056">
@@ -21886,10 +21880,10 @@
         <v>2219</v>
       </c>
       <c r="C1056" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1056" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1057">
@@ -21900,10 +21894,10 @@
         <v>2221</v>
       </c>
       <c r="C1057" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1057" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1058">
@@ -21914,7 +21908,7 @@
         <v>2223</v>
       </c>
       <c r="C1058" t="s">
-        <v>6</v>
+        <v>1725</v>
       </c>
       <c r="D1058" t="s">
         <v>7</v>
@@ -21928,10 +21922,10 @@
         <v>2225</v>
       </c>
       <c r="C1059" t="s">
-        <v>1725</v>
+        <v>1194</v>
       </c>
       <c r="D1059" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1060">
@@ -21942,10 +21936,10 @@
         <v>2227</v>
       </c>
       <c r="C1060" t="s">
-        <v>1194</v>
+        <v>6</v>
       </c>
       <c r="D1060" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1061">
@@ -21956,10 +21950,10 @@
         <v>2229</v>
       </c>
       <c r="C1061" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1061" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1062">
@@ -21970,10 +21964,10 @@
         <v>2231</v>
       </c>
       <c r="C1062" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D1062" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1063">
@@ -21984,10 +21978,10 @@
         <v>2233</v>
       </c>
       <c r="C1063" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D1063" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1064">
@@ -21998,10 +21992,10 @@
         <v>2235</v>
       </c>
       <c r="C1064" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="D1064" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1065">
@@ -22012,7 +22006,7 @@
         <v>2237</v>
       </c>
       <c r="C1065" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="D1065" t="s">
         <v>7</v>
@@ -22026,10 +22020,10 @@
         <v>2239</v>
       </c>
       <c r="C1066" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D1066" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1067">
@@ -22040,10 +22034,10 @@
         <v>2241</v>
       </c>
       <c r="C1067" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1067" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1068">
@@ -22068,7 +22062,7 @@
         <v>2245</v>
       </c>
       <c r="C1069" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D1069" t="s">
         <v>7</v>
@@ -22082,7 +22076,7 @@
         <v>2247</v>
       </c>
       <c r="C1070" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D1070" t="s">
         <v>7</v>
@@ -22127,20 +22121,6 @@
         <v>6</v>
       </c>
       <c r="D1073" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="s">
-        <v>2254</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>2255</v>
-      </c>
-      <c r="C1074" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1074" t="s">
         <v>7</v>
       </c>
     </row>
